--- a/tools/importer/reports/import-blog-article.report.xlsx
+++ b/tools/importer/reports/import-blog-article.report.xlsx
@@ -73,7 +73,7 @@
     <t>blog-article</t>
   </si>
   <si>
-    <t>2026-05-05T17:49:44.812Z</t>
+    <t>2026-05-05T18:10:18.912Z</t>
   </si>
   <si>
     <t>Protecting yourself from online scams and fraud | AA Insurance</t>
